--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/TransparentBackgroundFill/TransparentBackgroundFill.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/TransparentBackgroundFill/TransparentBackgroundFill.xlsx
@@ -401,14 +401,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:B14"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.570312" style="3" customWidth="1"/>
-    <x:col min="2" max="16384" width="9" style="3" customWidth="1"/>
+    <x:col min="2" max="16384" width="9" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="18" customHeight="1" s="0" customFormat="1">
@@ -451,10 +449,7 @@
       <x:formula>5</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/TransparentBackgroundFill/TransparentBackgroundFill.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/TransparentBackgroundFill/TransparentBackgroundFill.xlsx
@@ -405,8 +405,8 @@
   <x:dimension ref="A1:B14"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.570312" style="3" customWidth="1"/>
-    <x:col min="2" max="16384" width="9" style="3"/>
+    <x:col min="1" max="1" width="9.5703125" style="2" customWidth="1"/>
+    <x:col min="2" max="16384" width="9" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1" ht="18" customHeight="1" s="0" customFormat="1">
